--- a/Result/profitability/8183.xlsx
+++ b/Result/profitability/8183.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.58125</v>
       </c>
       <c r="N2" t="n">
-        <v>11.74625</v>
+        <v>11.73125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3925</v>
+        <v>0.29875</v>
       </c>
       <c r="N3" t="n">
-        <v>10.32</v>
+        <v>10.3575</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.145</v>
+        <v>0.22125</v>
       </c>
       <c r="N4" t="n">
-        <v>8.84625</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01125000000000004</v>
+        <v>0.10125</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2825</v>
+        <v>7.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05375000000000002</v>
+        <v>-0.08500000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>6.266249999999999</v>
+        <v>5.9475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.43125</v>
+        <v>-0.5175000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.23</v>
+        <v>4.055</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5774999999999999</v>
+        <v>-0.5225</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2675</v>
+        <v>3.38625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6037499999999999</v>
+        <v>-0.60375</v>
       </c>
       <c r="N9" t="n">
         <v>2.72625</v>
@@ -1899,7 +1899,7 @@
         <v>0.03</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3737499999999999</v>
+        <v>-0.37375</v>
       </c>
       <c r="N12" t="n">
         <v>4.645</v>
@@ -2026,7 +2026,7 @@
         <v>-0.06</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2412499999999999</v>
+        <v>-0.24125</v>
       </c>
       <c r="N13" t="n">
         <v>5.697500000000001</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2182</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1899</v>
+      </c>
+      <c r="E75" t="n">
+        <v>283</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>77</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>103</v>
+      </c>
+      <c r="K75" t="n">
+        <v>89</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.69625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.85125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9500000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07903494176372727</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.2200000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01725490196078439</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
